--- a/incoming-freightiq/CE & SF Combined_Profit and Loss (16).xlsx
+++ b/incoming-freightiq/CE & SF Combined_Profit and Loss (16).xlsx
@@ -33,7 +33,7 @@
     <t>Profit and Loss</t>
   </si>
   <si>
-    <t>January 1-May 25, 2026</t>
+    <t>January 1-May 30, 2026</t>
   </si>
   <si>
     <t>Income</t>
@@ -480,13 +480,13 @@
     <t>May 18-24 2026</t>
   </si>
   <si>
-    <t>May 25-25 2026</t>
+    <t>May 25-30 2026</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>Accrual Basis Tuesday, May 26, 2026 01:02 AM GMTZ</t>
+    <t>Accrual Basis Saturday, May 30, 2026 04:44 PM GMTZ</t>
   </si>
 </sst>
 </file>
@@ -1175,9 +1175,7 @@
     <col min="18" max="18" width="16.125" style="43" customWidth="1"/>
     <col min="19" max="19" width="17" style="43" customWidth="1"/>
     <col min="20" max="20" width="15.25" style="43" customWidth="1"/>
-    <col min="21" max="22" width="16.125" style="43" customWidth="1"/>
-    <col min="23" max="23" width="12.625" style="43" customWidth="1"/>
-    <col min="24" max="24" width="16.125" style="43" customWidth="1"/>
+    <col min="21" max="24" width="16.125" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="16">
@@ -1337,10 +1335,12 @@
       <c r="V7" s="47">
         <v>21779.35</v>
       </c>
-      <c r="W7" s="46"/>
+      <c r="W7" s="47">
+        <v>41827.25</v>
+      </c>
       <c r="X7" s="47">
         <f>B7+C7+D7+E7+F7+G7+H7+I7+J7+K7+L7+M7+N7+O7+P7+Q7+R7+S7+T7+U7+V7+W7</f>
-        <v>286492.16</v>
+        <v>328319.41</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="16">
@@ -1410,10 +1410,12 @@
       <c r="V8" s="47">
         <v>619783.65</v>
       </c>
-      <c r="W8" s="46"/>
+      <c r="W8" s="47">
+        <v>235869.96</v>
+      </c>
       <c r="X8" s="47">
         <f>B8+C8+D8+E8+F8+G8+H8+I8+J8+K8+L8+M8+N8+O8+P8+Q8+R8+S8+T8+U8+V8+W8</f>
-        <v>6621776.210000001</v>
+        <v>6857646.170000001</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="16">
@@ -1477,10 +1479,12 @@
       <c r="V9" s="47">
         <v>945.86</v>
       </c>
-      <c r="W9" s="46"/>
+      <c r="W9" s="47">
+        <v>15832.86</v>
+      </c>
       <c r="X9" s="47">
         <f>B9+C9+D9+E9+F9+G9+H9+I9+J9+K9+L9+M9+N9+O9+P9+Q9+R9+S9+T9+U9+V9+W9</f>
-        <v>43102.19</v>
+        <v>58935.05</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="16">
@@ -1550,10 +1554,12 @@
       <c r="V10" s="47">
         <v>141802.81</v>
       </c>
-      <c r="W10" s="46"/>
+      <c r="W10" s="47">
+        <v>145103.06</v>
+      </c>
       <c r="X10" s="47">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10+L10+M10+N10+O10+P10+Q10+R10+S10+T10+U10+V10+W10</f>
-        <v>2387227.07</v>
+        <v>2532330.13</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="16">
@@ -1644,13 +1650,13 @@
         <f>V6+V7+V8+V9+V10</f>
         <v>784311.6699999999</v>
       </c>
-      <c r="W11" s="49">
+      <c r="W11" s="48">
         <f>W6+W7+W8+W9+W10</f>
-        <v>0.0</v>
+        <v>438633.12999999995</v>
       </c>
       <c r="X11" s="49">
         <f>B11+C11+D11+E11+F11+G11+H11+I11+J11+K11+L11+M11+N11+O11+P11+Q11+R11+S11+T11+U11+V11+W11</f>
-        <v>9338597.63</v>
+        <v>9777230.760000002</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="16">
@@ -1745,12 +1751,14 @@
         <v>431256.0</v>
       </c>
       <c r="V13" s="47">
-        <v>402465.27</v>
-      </c>
-      <c r="W13" s="46"/>
+        <v>403415.27</v>
+      </c>
+      <c r="W13" s="47">
+        <v>178132.0</v>
+      </c>
       <c r="X13" s="47">
         <f>B13+C13+D13+E13+F13+G13+H13+I13+J13+K13+L13+M13+N13+O13+P13+Q13+R13+S13+T13+U13+V13+W13</f>
-        <v>4762427.84</v>
+        <v>4941509.84</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="16">
@@ -1798,10 +1806,12 @@
       <c r="V14" s="47">
         <v>1707.35</v>
       </c>
-      <c r="W14" s="46"/>
+      <c r="W14" s="47">
+        <v>1729.07</v>
+      </c>
       <c r="X14" s="47">
         <f>B14+C14+D14+E14+F14+G14+H14+I14+J14+K14+L14+M14+N14+O14+P14+Q14+R14+S14+T14+U14+V14+W14</f>
-        <v>17943.3</v>
+        <v>19672.37</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="16">
@@ -1943,15 +1953,15 @@
       </c>
       <c r="V16" s="48">
         <f>V12+V13+V14+V15</f>
-        <v>404172.62</v>
-      </c>
-      <c r="W16" s="49">
+        <v>405122.62</v>
+      </c>
+      <c r="W16" s="48">
         <f>W12+W13+W14+W15</f>
-        <v>0.0</v>
+        <v>179861.07</v>
       </c>
       <c r="X16" s="49">
         <f>B16+C16+D16+E16+F16+G16+H16+I16+J16+K16+L16+M16+N16+O16+P16+Q16+R16+S16+T16+U16+V16+W16</f>
-        <v>4835450.74</v>
+        <v>5016261.8100000005</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="16">
@@ -2040,15 +2050,15 @@
       </c>
       <c r="V17" s="48">
         <f>V11-V16</f>
-        <v>380139.04999999993</v>
-      </c>
-      <c r="W17" s="49">
+        <v>379189.04999999993</v>
+      </c>
+      <c r="W17" s="48">
         <f>W11-W16</f>
-        <v>0.0</v>
+        <v>258772.05999999994</v>
       </c>
       <c r="X17" s="49">
         <f>B17+C17+D17+E17+F17+G17+H17+I17+J17+K17+L17+M17+N17+O17+P17+Q17+R17+S17+T17+U17+V17+W17</f>
-        <v>4503146.89</v>
+        <v>4760968.949999999</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="16">
@@ -2143,12 +2153,14 @@
         <v>4334.14</v>
       </c>
       <c r="V19" s="47">
-        <v>2187.69</v>
-      </c>
-      <c r="W19" s="46"/>
+        <v>3699.11</v>
+      </c>
+      <c r="W19" s="47">
+        <v>2790.71</v>
+      </c>
       <c r="X19" s="47">
         <f>B19+C19+D19+E19+F19+G19+H19+I19+J19+K19+L19+M19+N19+O19+P19+Q19+R19+S19+T19+U19+V19+W19</f>
-        <v>52839.73</v>
+        <v>57141.86</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="16">
@@ -2518,10 +2530,12 @@
       <c r="T29" s="46"/>
       <c r="U29" s="46"/>
       <c r="V29" s="46"/>
-      <c r="W29" s="46"/>
+      <c r="W29" s="47">
+        <v>665.67</v>
+      </c>
       <c r="X29" s="47">
         <f>B29+C29+D29+E29+F29+G29+H29+I29+J29+K29+L29+M29+N29+O29+P29+Q29+R29+S29+T29+U29+V29+W29</f>
-        <v>4345.09</v>
+        <v>5010.76</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="16">
@@ -2612,13 +2626,13 @@
         <f>V21+V22+V23+V24+V25+V26+V27+V28+V29</f>
         <v>33193.46</v>
       </c>
-      <c r="W30" s="49">
+      <c r="W30" s="48">
         <f>W21+W22+W23+W24+W25+W26+W27+W28+W29</f>
-        <v>0.0</v>
+        <v>665.67</v>
       </c>
       <c r="X30" s="49">
         <f>B30+C30+D30+E30+F30+G30+H30+I30+J30+K30+L30+M30+N30+O30+P30+Q30+R30+S30+T30+U30+V30+W30</f>
-        <v>74958.98999999999</v>
+        <v>75624.65999999999</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="16">
@@ -2760,10 +2774,12 @@
       <c r="T34" s="46"/>
       <c r="U34" s="46"/>
       <c r="V34" s="46"/>
-      <c r="W34" s="46"/>
+      <c r="W34" s="47">
+        <v>6500.0</v>
+      </c>
       <c r="X34" s="47">
         <f>B34+C34+D34+E34+F34+G34+H34+I34+J34+K34+L34+M34+N34+O34+P34+Q34+R34+S34+T34+U34+V34+W34</f>
-        <v>66000.0</v>
+        <v>72500.0</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="16">
@@ -2854,13 +2870,13 @@
         <f>V31+V32+V33+V34</f>
         <v>3000.0</v>
       </c>
-      <c r="W35" s="49">
+      <c r="W35" s="48">
         <f>W31+W32+W33+W34</f>
-        <v>0.0</v>
+        <v>6500.0</v>
       </c>
       <c r="X35" s="49">
         <f>B35+C35+D35+E35+F35+G35+H35+I35+J35+K35+L35+M35+N35+O35+P35+Q35+R35+S35+T35+U35+V35+W35</f>
-        <v>87000.0</v>
+        <v>93500.0</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="16">
@@ -2930,10 +2946,12 @@
       <c r="V36" s="47">
         <v>124.0</v>
       </c>
-      <c r="W36" s="46"/>
+      <c r="W36" s="47">
+        <v>128.5</v>
+      </c>
       <c r="X36" s="47">
         <f>B36+C36+D36+E36+F36+G36+H36+I36+J36+K36+L36+M36+N36+O36+P36+Q36+R36+S36+T36+U36+V36+W36</f>
-        <v>3434.64</v>
+        <v>3563.14</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="16">
@@ -3036,10 +3054,12 @@
         <v>2041.31</v>
       </c>
       <c r="V39" s="46"/>
-      <c r="W39" s="46"/>
+      <c r="W39" s="47">
+        <v>2041.31</v>
+      </c>
       <c r="X39" s="47">
         <f>B39+C39+D39+E39+F39+G39+H39+I39+J39+K39+L39+M39+N39+O39+P39+Q39+R39+S39+T39+U39+V39+W39</f>
-        <v>6347.0599999999995</v>
+        <v>8388.369999999999</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="16">
@@ -3142,10 +3162,12 @@
       <c r="V41" s="47">
         <v>1000.0</v>
       </c>
-      <c r="W41" s="46"/>
+      <c r="W41" s="47">
+        <v>1000.0</v>
+      </c>
       <c r="X41" s="47">
         <f>B41+C41+D41+E41+F41+G41+H41+I41+J41+K41+L41+M41+N41+O41+P41+Q41+R41+S41+T41+U41+V41+W41</f>
-        <v>20000.0</v>
+        <v>21000.0</v>
       </c>
     </row>
     <row r="42" spans="1:24" ht="16">
@@ -3347,10 +3369,12 @@
         <v>5655.0</v>
       </c>
       <c r="V46" s="46"/>
-      <c r="W46" s="46"/>
+      <c r="W46" s="47">
+        <v>4166.0</v>
+      </c>
       <c r="X46" s="47">
         <f>B46+C46+D46+E46+F46+G46+H46+I46+J46+K46+L46+M46+N46+O46+P46+Q46+R46+S46+T46+U46+V46+W46</f>
-        <v>47848.0</v>
+        <v>52014.0</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="16">
@@ -3739,13 +3763,13 @@
         <f>V38+V39+V40+V41+V42+V43+V44+V45+V46+V47+V52+V53</f>
         <v>11000.0</v>
       </c>
-      <c r="W54" s="49">
+      <c r="W54" s="48">
         <f>W38+W39+W40+W41+W42+W43+W44+W45+W46+W47+W52+W53</f>
-        <v>0.0</v>
+        <v>7207.3099999999995</v>
       </c>
       <c r="X54" s="49">
         <f>B54+C54+D54+E54+F54+G54+H54+I54+J54+K54+L54+M54+N54+O54+P54+Q54+R54+S54+T54+U54+V54+W54</f>
-        <v>133571.85</v>
+        <v>140779.16</v>
       </c>
     </row>
     <row r="55" spans="1:24" ht="16">
@@ -3815,10 +3839,12 @@
       <c r="V55" s="47">
         <v>96.75</v>
       </c>
-      <c r="W55" s="46"/>
+      <c r="W55" s="47">
+        <v>193.5</v>
+      </c>
       <c r="X55" s="47">
         <f>B55+C55+D55+E55+F55+G55+H55+I55+J55+K55+L55+M55+N55+O55+P55+Q55+R55+S55+T55+U55+V55+W55</f>
-        <v>3281.25</v>
+        <v>3474.75</v>
       </c>
     </row>
     <row r="56" spans="1:24" ht="16">
@@ -3856,10 +3882,12 @@
       <c r="V56" s="47">
         <v>40.39</v>
       </c>
-      <c r="W56" s="46"/>
+      <c r="W56" s="47">
+        <v>22.96</v>
+      </c>
       <c r="X56" s="47">
         <f>B56+C56+D56+E56+F56+G56+H56+I56+J56+K56+L56+M56+N56+O56+P56+Q56+R56+S56+T56+U56+V56+W56</f>
-        <v>180.95</v>
+        <v>203.91</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="16">
@@ -3901,10 +3929,12 @@
       <c r="T57" s="46"/>
       <c r="U57" s="46"/>
       <c r="V57" s="46"/>
-      <c r="W57" s="46"/>
+      <c r="W57" s="47">
+        <v>20000.0</v>
+      </c>
       <c r="X57" s="47">
         <f>B57+C57+D57+E57+F57+G57+H57+I57+J57+K57+L57+M57+N57+O57+P57+Q57+R57+S57+T57+U57+V57+W57</f>
-        <v>3340.65</v>
+        <v>23340.65</v>
       </c>
     </row>
     <row r="58" spans="1:24" ht="16">
@@ -3972,12 +4002,14 @@
         <v>4104.55</v>
       </c>
       <c r="V58" s="47">
-        <v>2242.59</v>
-      </c>
-      <c r="W58" s="46"/>
+        <v>2523.59</v>
+      </c>
+      <c r="W58" s="47">
+        <v>6008.15</v>
+      </c>
       <c r="X58" s="47">
         <f>B58+C58+D58+E58+F58+G58+H58+I58+J58+K58+L58+M58+N58+O58+P58+Q58+R58+S58+T58+U58+V58+W58</f>
-        <v>74736.90000000001</v>
+        <v>81026.05</v>
       </c>
     </row>
     <row r="59" spans="1:24" ht="16">
@@ -4035,10 +4067,12 @@
       <c r="V59" s="47">
         <v>160.0</v>
       </c>
-      <c r="W59" s="46"/>
+      <c r="W59" s="47">
+        <v>180.0</v>
+      </c>
       <c r="X59" s="47">
         <f>B59+C59+D59+E59+F59+G59+H59+I59+J59+K59+L59+M59+N59+O59+P59+Q59+R59+S59+T59+U59+V59+W59</f>
-        <v>14610.06</v>
+        <v>14790.06</v>
       </c>
     </row>
     <row r="60" spans="1:24" ht="16">
@@ -4096,10 +4130,12 @@
       <c r="V60" s="47">
         <v>14420.0</v>
       </c>
-      <c r="W60" s="46"/>
+      <c r="W60" s="47">
+        <v>17392.5</v>
+      </c>
       <c r="X60" s="47">
         <f>B60+C60+D60+E60+F60+G60+H60+I60+J60+K60+L60+M60+N60+O60+P60+Q60+R60+S60+T60+U60+V60+W60</f>
-        <v>82233.8</v>
+        <v>99626.3</v>
       </c>
     </row>
     <row r="61" spans="1:24" ht="16">
@@ -4190,13 +4226,13 @@
         <f>V59+V60</f>
         <v>14580.0</v>
       </c>
-      <c r="W61" s="49">
+      <c r="W61" s="48">
         <f>W59+W60</f>
-        <v>0.0</v>
+        <v>17572.5</v>
       </c>
       <c r="X61" s="49">
         <f>B61+C61+D61+E61+F61+G61+H61+I61+J61+K61+L61+M61+N61+O61+P61+Q61+R61+S61+T61+U61+V61+W61</f>
-        <v>96843.86</v>
+        <v>114416.36</v>
       </c>
     </row>
     <row r="62" spans="1:24" ht="16">
@@ -4264,12 +4300,14 @@
         <v>372.45</v>
       </c>
       <c r="V62" s="47">
-        <v>486.44</v>
-      </c>
-      <c r="W62" s="46"/>
+        <v>1118.72</v>
+      </c>
+      <c r="W62" s="47">
+        <v>300.0</v>
+      </c>
       <c r="X62" s="47">
         <f>B62+C62+D62+E62+F62+G62+H62+I62+J62+K62+L62+M62+N62+O62+P62+Q62+R62+S62+T62+U62+V62+W62</f>
-        <v>16542.81</v>
+        <v>17475.09</v>
       </c>
     </row>
     <row r="63" spans="1:24" ht="16">
@@ -4419,10 +4457,12 @@
       </c>
       <c r="U65" s="46"/>
       <c r="V65" s="46"/>
-      <c r="W65" s="46"/>
+      <c r="W65" s="47">
+        <v>160.55</v>
+      </c>
       <c r="X65" s="47">
         <f>B65+C65+D65+E65+F65+G65+H65+I65+J65+K65+L65+M65+N65+O65+P65+Q65+R65+S65+T65+U65+V65+W65</f>
-        <v>3277.9300000000003</v>
+        <v>3438.4800000000005</v>
       </c>
     </row>
     <row r="66" spans="1:24" ht="16">
@@ -4567,11 +4607,13 @@
         <v>1603.95</v>
       </c>
       <c r="U69" s="46"/>
-      <c r="V69" s="46"/>
+      <c r="V69" s="47">
+        <v>1818.0</v>
+      </c>
       <c r="W69" s="46"/>
       <c r="X69" s="47">
         <f>B69+C69+D69+E69+F69+G69+H69+I69+J69+K69+L69+M69+N69+O69+P69+Q69+R69+S69+T69+U69+V69+W69</f>
-        <v>3982.92</v>
+        <v>5800.92</v>
       </c>
     </row>
     <row r="70" spans="1:24" ht="16">
@@ -4758,10 +4800,12 @@
       <c r="V73" s="47">
         <v>16.88</v>
       </c>
-      <c r="W73" s="46"/>
+      <c r="W73" s="47">
+        <v>10.36</v>
+      </c>
       <c r="X73" s="47">
         <f>B73+C73+D73+E73+F73+G73+H73+I73+J73+K73+L73+M73+N73+O73+P73+Q73+R73+S73+T73+U73+V73+W73</f>
-        <v>21958.55</v>
+        <v>21968.91</v>
       </c>
     </row>
     <row r="74" spans="1:24" ht="16">
@@ -4850,15 +4894,15 @@
       </c>
       <c r="V74" s="48">
         <f>V66+V67+V68+V69+V70+V71+V72+V73</f>
-        <v>5826.530000000001</v>
-      </c>
-      <c r="W74" s="49">
+        <v>7644.530000000001</v>
+      </c>
+      <c r="W74" s="48">
         <f>W66+W67+W68+W69+W70+W71+W72+W73</f>
-        <v>0.0</v>
+        <v>10.36</v>
       </c>
       <c r="X74" s="49">
         <f>B74+C74+D74+E74+F74+G74+H74+I74+J74+K74+L74+M74+N74+O74+P74+Q74+R74+S74+T74+U74+V74+W74</f>
-        <v>86020.99</v>
+        <v>87849.35</v>
       </c>
     </row>
     <row r="75" spans="1:24" ht="16">
@@ -4941,12 +4985,12 @@
         <v>1421.0</v>
       </c>
       <c r="V76" s="47">
-        <v>109.0</v>
+        <v>218.0</v>
       </c>
       <c r="W76" s="46"/>
       <c r="X76" s="47">
         <f>B76+C76+D76+E76+F76+G76+H76+I76+J76+K76+L76+M76+N76+O76+P76+Q76+R76+S76+T76+U76+V76+W76</f>
-        <v>8900.5</v>
+        <v>9009.5</v>
       </c>
     </row>
     <row r="77" spans="1:24" ht="16">
@@ -5021,10 +5065,12 @@
       </c>
       <c r="U78" s="46"/>
       <c r="V78" s="46"/>
-      <c r="W78" s="46"/>
+      <c r="W78" s="47">
+        <v>1900.0</v>
+      </c>
       <c r="X78" s="47">
         <f>B78+C78+D78+E78+F78+G78+H78+I78+J78+K78+L78+M78+N78+O78+P78+Q78+R78+S78+T78+U78+V78+W78</f>
-        <v>27700.0</v>
+        <v>29600.0</v>
       </c>
     </row>
     <row r="79" spans="1:24" ht="16">
@@ -5092,10 +5138,12 @@
       <c r="V79" s="47">
         <v>288.46</v>
       </c>
-      <c r="W79" s="46"/>
+      <c r="W79" s="47">
+        <v>288.46</v>
+      </c>
       <c r="X79" s="47">
         <f>B79+C79+D79+E79+F79+G79+H79+I79+J79+K79+L79+M79+N79+O79+P79+Q79+R79+S79+T79+U79+V79+W79</f>
-        <v>5769.2</v>
+        <v>6057.66</v>
       </c>
     </row>
     <row r="80" spans="1:24" ht="16">
@@ -5147,10 +5195,12 @@
       <c r="V80" s="47">
         <v>2500.0</v>
       </c>
-      <c r="W80" s="46"/>
+      <c r="W80" s="47">
+        <v>7809.01</v>
+      </c>
       <c r="X80" s="47">
         <f>B80+C80+D80+E80+F80+G80+H80+I80+J80+K80+L80+M80+N80+O80+P80+Q80+R80+S80+T80+U80+V80+W80</f>
-        <v>25295.0</v>
+        <v>33104.01</v>
       </c>
     </row>
     <row r="81" spans="1:24" ht="16">
@@ -5239,15 +5289,15 @@
       </c>
       <c r="V81" s="48">
         <f>V76+V77+V78+V79+V80</f>
-        <v>2897.46</v>
-      </c>
-      <c r="W81" s="49">
+        <v>3006.46</v>
+      </c>
+      <c r="W81" s="48">
         <f>W76+W77+W78+W79+W80</f>
-        <v>0.0</v>
+        <v>9997.470000000001</v>
       </c>
       <c r="X81" s="49">
         <f>B81+C81+D81+E81+F81+G81+H81+I81+J81+K81+L81+M81+N81+O81+P81+Q81+R81+S81+T81+U81+V81+W81</f>
-        <v>69014.7</v>
+        <v>79121.17</v>
       </c>
     </row>
     <row r="82" spans="1:24" ht="16">
@@ -5291,10 +5341,12 @@
       <c r="T82" s="46"/>
       <c r="U82" s="46"/>
       <c r="V82" s="46"/>
-      <c r="W82" s="46"/>
+      <c r="W82" s="47">
+        <v>375.6</v>
+      </c>
       <c r="X82" s="47">
         <f>B82+C82+D82+E82+F82+G82+H82+I82+J82+K82+L82+M82+N82+O82+P82+Q82+R82+S82+T82+U82+V82+W82</f>
-        <v>3271.2599999999998</v>
+        <v>3646.8599999999997</v>
       </c>
     </row>
     <row r="83" spans="1:24" ht="16">
@@ -5344,10 +5396,12 @@
       </c>
       <c r="U83" s="46"/>
       <c r="V83" s="46"/>
-      <c r="W83" s="46"/>
+      <c r="W83" s="47">
+        <v>502.09</v>
+      </c>
       <c r="X83" s="47">
         <f>B83+C83+D83+E83+F83+G83+H83+I83+J83+K83+L83+M83+N83+O83+P83+Q83+R83+S83+T83+U83+V83+W83</f>
-        <v>4173.14</v>
+        <v>4675.2300000000005</v>
       </c>
     </row>
     <row r="84" spans="1:24" ht="16">
@@ -5443,12 +5497,14 @@
         <v>4439.98</v>
       </c>
       <c r="V85" s="47">
-        <v>2847.65</v>
-      </c>
-      <c r="W85" s="46"/>
+        <v>3363.1</v>
+      </c>
+      <c r="W85" s="47">
+        <v>9445.12</v>
+      </c>
       <c r="X85" s="47">
         <f>B85+C85+D85+E85+F85+G85+H85+I85+J85+K85+L85+M85+N85+O85+P85+Q85+R85+S85+T85+U85+V85+W85</f>
-        <v>79986.57999999999</v>
+        <v>89947.15</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="16">
@@ -5516,10 +5572,12 @@
       <c r="V86" s="47">
         <v>10625.0</v>
       </c>
-      <c r="W86" s="46"/>
+      <c r="W86" s="47">
+        <v>6625.0</v>
+      </c>
       <c r="X86" s="47">
         <f>B86+C86+D86+E86+F86+G86+H86+I86+J86+K86+L86+M86+N86+O86+P86+Q86+R86+S86+T86+U86+V86+W86</f>
-        <v>178260.52000000002</v>
+        <v>184885.52000000002</v>
       </c>
     </row>
     <row r="87" spans="1:24" ht="16">
@@ -5641,15 +5699,15 @@
       </c>
       <c r="V88" s="48">
         <f>V84+V85+V86+V87</f>
-        <v>13472.65</v>
-      </c>
-      <c r="W88" s="49">
+        <v>13988.1</v>
+      </c>
+      <c r="W88" s="48">
         <f>W84+W85+W86+W87</f>
-        <v>0.0</v>
+        <v>16070.12</v>
       </c>
       <c r="X88" s="49">
         <f>B88+C88+D88+E88+F88+G88+H88+I88+J88+K88+L88+M88+N88+O88+P88+Q88+R88+S88+T88+U88+V88+W88</f>
-        <v>261155.66000000003</v>
+        <v>277741.23000000004</v>
       </c>
     </row>
     <row r="89" spans="1:24" ht="16">
@@ -5750,12 +5808,14 @@
         <v>1037.07</v>
       </c>
       <c r="V90" s="47">
-        <v>1466.32</v>
-      </c>
-      <c r="W90" s="46"/>
+        <v>1502.0</v>
+      </c>
+      <c r="W90" s="47">
+        <v>922.62</v>
+      </c>
       <c r="X90" s="47">
         <f>B90+C90+D90+E90+F90+G90+H90+I90+J90+K90+L90+M90+N90+O90+P90+Q90+R90+S90+T90+U90+V90+W90</f>
-        <v>20776.79</v>
+        <v>21735.09</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="16">
@@ -5799,10 +5859,12 @@
       <c r="V91" s="47">
         <v>21887.67</v>
       </c>
-      <c r="W91" s="46"/>
+      <c r="W91" s="47">
+        <v>18437.87</v>
+      </c>
       <c r="X91" s="47">
         <f>B91+C91+D91+E91+F91+G91+H91+I91+J91+K91+L91+M91+N91+O91+P91+Q91+R91+S91+T91+U91+V91+W91</f>
-        <v>90044.76</v>
+        <v>108482.62999999999</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="16">
@@ -5842,10 +5904,12 @@
         <v>700.0</v>
       </c>
       <c r="V92" s="46"/>
-      <c r="W92" s="46"/>
+      <c r="W92" s="47">
+        <v>983.3</v>
+      </c>
       <c r="X92" s="47">
         <f>B92+C92+D92+E92+F92+G92+H92+I92+J92+K92+L92+M92+N92+O92+P92+Q92+R92+S92+T92+U92+V92+W92</f>
-        <v>6614.34</v>
+        <v>7597.64</v>
       </c>
     </row>
     <row r="93" spans="1:24" ht="16">
@@ -5926,11 +5990,13 @@
       <c r="U94" s="47">
         <v>1718.63</v>
       </c>
-      <c r="V94" s="46"/>
+      <c r="V94" s="47">
+        <v>1617.65</v>
+      </c>
       <c r="W94" s="46"/>
       <c r="X94" s="47">
         <f>B94+C94+D94+E94+F94+G94+H94+I94+J94+K94+L94+M94+N94+O94+P94+Q94+R94+S94+T94+U94+V94+W94</f>
-        <v>31962.95</v>
+        <v>33580.6</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="16">
@@ -5998,12 +6064,14 @@
         <v>214.72</v>
       </c>
       <c r="V95" s="47">
-        <v>214.72</v>
-      </c>
-      <c r="W95" s="46"/>
+        <v>406.37</v>
+      </c>
+      <c r="W95" s="47">
+        <v>23.07</v>
+      </c>
       <c r="X95" s="47">
         <f>B95+C95+D95+E95+F95+G95+H95+I95+J95+K95+L95+M95+N95+O95+P95+Q95+R95+S95+T95+U95+V95+W95</f>
-        <v>4317.469999999998</v>
+        <v>4532.189999999998</v>
       </c>
     </row>
     <row r="96" spans="1:24" ht="16">
@@ -6071,10 +6139,12 @@
       <c r="V96" s="47">
         <v>16064.97</v>
       </c>
-      <c r="W96" s="46"/>
+      <c r="W96" s="47">
+        <v>17585.36</v>
+      </c>
       <c r="X96" s="47">
         <f>B96+C96+D96+E96+F96+G96+H96+I96+J96+K96+L96+M96+N96+O96+P96+Q96+R96+S96+T96+U96+V96+W96</f>
-        <v>268293.91</v>
+        <v>285879.26999999996</v>
       </c>
     </row>
     <row r="97" spans="1:24" ht="16">
@@ -6144,10 +6214,12 @@
       <c r="V97" s="47">
         <v>16727.92</v>
       </c>
-      <c r="W97" s="46"/>
+      <c r="W97" s="47">
+        <v>15949.23</v>
+      </c>
       <c r="X97" s="47">
         <f>B97+C97+D97+E97+F97+G97+H97+I97+J97+K97+L97+M97+N97+O97+P97+Q97+R97+S97+T97+U97+V97+W97</f>
-        <v>258184.75</v>
+        <v>274133.98</v>
       </c>
     </row>
     <row r="98" spans="1:24" ht="16">
@@ -6426,13 +6498,13 @@
         <f>V97+V98+V99+V100+V101</f>
         <v>16727.92</v>
       </c>
-      <c r="W102" s="49">
+      <c r="W102" s="48">
         <f>W97+W98+W99+W100+W101</f>
-        <v>0.0</v>
+        <v>15949.23</v>
       </c>
       <c r="X102" s="49">
         <f>B102+C102+D102+E102+F102+G102+H102+I102+J102+K102+L102+M102+N102+O102+P102+Q102+R102+S102+T102+U102+V102+W102</f>
-        <v>309585.95</v>
+        <v>325535.18</v>
       </c>
     </row>
     <row r="103" spans="1:24" ht="16">
@@ -6502,10 +6574,12 @@
       <c r="V103" s="47">
         <v>43590.5</v>
       </c>
-      <c r="W103" s="46"/>
+      <c r="W103" s="47">
+        <v>41186.97</v>
+      </c>
       <c r="X103" s="47">
         <f>B103+C103+D103+E103+F103+G103+H103+I103+J103+K103+L103+M103+N103+O103+P103+Q103+R103+S103+T103+U103+V103+W103</f>
-        <v>635718.93</v>
+        <v>676905.9</v>
       </c>
     </row>
     <row r="104" spans="1:24" ht="16">
@@ -6575,10 +6649,12 @@
       <c r="V104" s="47">
         <v>13176.99</v>
       </c>
-      <c r="W104" s="46"/>
+      <c r="W104" s="47">
+        <v>12410.31</v>
+      </c>
       <c r="X104" s="47">
         <f>B104+C104+D104+E104+F104+G104+H104+I104+J104+K104+L104+M104+N104+O104+P104+Q104+R104+S104+T104+U104+V104+W104</f>
-        <v>263478.07000000007</v>
+        <v>275888.38000000006</v>
       </c>
     </row>
     <row r="105" spans="1:24" ht="16">
@@ -6667,15 +6743,15 @@
       </c>
       <c r="V105" s="48">
         <f>V93+V94+V95+V96+V102+V103+V104</f>
-        <v>89775.1</v>
-      </c>
-      <c r="W105" s="49">
+        <v>91584.40000000001</v>
+      </c>
+      <c r="W105" s="48">
         <f>W93+W94+W95+W96+W102+W103+W104</f>
-        <v>0.0</v>
+        <v>87154.94</v>
       </c>
       <c r="X105" s="49">
         <f>B105+C105+D105+E105+F105+G105+H105+I105+J105+K105+L105+M105+N105+O105+P105+Q105+R105+S105+T105+U105+V105+W105</f>
-        <v>1513357.2800000003</v>
+        <v>1602321.52</v>
       </c>
     </row>
     <row r="106" spans="1:24" ht="16">
@@ -6739,10 +6815,12 @@
       <c r="V106" s="47">
         <v>905.85</v>
       </c>
-      <c r="W106" s="46"/>
+      <c r="W106" s="47">
+        <v>718.63</v>
+      </c>
       <c r="X106" s="47">
         <f>B106+C106+D106+E106+F106+G106+H106+I106+J106+K106+L106+M106+N106+O106+P106+Q106+R106+S106+T106+U106+V106+W106</f>
-        <v>6450.97</v>
+        <v>7169.6</v>
       </c>
     </row>
     <row r="107" spans="1:24" ht="16">
@@ -6932,10 +7010,12 @@
       <c r="V110" s="47">
         <v>67.97</v>
       </c>
-      <c r="W110" s="46"/>
+      <c r="W110" s="47">
+        <v>32.75</v>
+      </c>
       <c r="X110" s="47">
         <f>B110+C110+D110+E110+F110+G110+H110+I110+J110+K110+L110+M110+N110+O110+P110+Q110+R110+S110+T110+U110+V110+W110</f>
-        <v>1837.6700000000003</v>
+        <v>1870.4200000000003</v>
       </c>
     </row>
     <row r="111" spans="1:24" ht="16">
@@ -7026,13 +7106,13 @@
         <f>V107+V108+V109+V110</f>
         <v>67.97</v>
       </c>
-      <c r="W111" s="49">
+      <c r="W111" s="48">
         <f>W107+W108+W109+W110</f>
-        <v>0.0</v>
+        <v>32.75</v>
       </c>
       <c r="X111" s="49">
         <f>B111+C111+D111+E111+F111+G111+H111+I111+J111+K111+L111+M111+N111+O111+P111+Q111+R111+S111+T111+U111+V111+W111</f>
-        <v>16129.789999999999</v>
+        <v>16162.539999999999</v>
       </c>
     </row>
     <row r="112" spans="1:24" ht="16">
@@ -7130,10 +7210,12 @@
       <c r="V113" s="47">
         <v>37153.46</v>
       </c>
-      <c r="W113" s="46"/>
+      <c r="W113" s="47">
+        <v>30641.42</v>
+      </c>
       <c r="X113" s="47">
         <f>B113+C113+D113+E113+F113+G113+H113+I113+J113+K113+L113+M113+N113+O113+P113+Q113+R113+S113+T113+U113+V113+W113</f>
-        <v>467943.81</v>
+        <v>498585.23</v>
       </c>
     </row>
     <row r="114" spans="1:24" ht="16">
@@ -7193,10 +7275,12 @@
       </c>
       <c r="U114" s="46"/>
       <c r="V114" s="46"/>
-      <c r="W114" s="46"/>
+      <c r="W114" s="47">
+        <v>19054.42</v>
+      </c>
       <c r="X114" s="47">
         <f>B114+C114+D114+E114+F114+G114+H114+I114+J114+K114+L114+M114+N114+O114+P114+Q114+R114+S114+T114+U114+V114+W114</f>
-        <v>128624.45</v>
+        <v>147678.87</v>
       </c>
     </row>
     <row r="115" spans="1:24" ht="16">
@@ -7250,10 +7334,12 @@
         <v>270.94</v>
       </c>
       <c r="V115" s="46"/>
-      <c r="W115" s="46"/>
+      <c r="W115" s="47">
+        <v>8550.0</v>
+      </c>
       <c r="X115" s="47">
         <f>B115+C115+D115+E115+F115+G115+H115+I115+J115+K115+L115+M115+N115+O115+P115+Q115+R115+S115+T115+U115+V115+W115</f>
-        <v>30839.62</v>
+        <v>39389.619999999995</v>
       </c>
     </row>
     <row r="116" spans="1:24" ht="16">
@@ -7356,10 +7442,12 @@
       <c r="V117" s="47">
         <v>13482.75</v>
       </c>
-      <c r="W117" s="46"/>
+      <c r="W117" s="47">
+        <v>8367.4</v>
+      </c>
       <c r="X117" s="47">
         <f>B117+C117+D117+E117+F117+G117+H117+I117+J117+K117+L117+M117+N117+O117+P117+Q117+R117+S117+T117+U117+V117+W117</f>
-        <v>152602.63</v>
+        <v>160970.03</v>
       </c>
     </row>
     <row r="118" spans="1:24" ht="16">
@@ -7468,10 +7556,12 @@
       <c r="V119" s="47">
         <v>10591.86</v>
       </c>
-      <c r="W119" s="46"/>
+      <c r="W119" s="47">
+        <v>83676.13</v>
+      </c>
       <c r="X119" s="47">
         <f>B119+C119+D119+E119+F119+G119+H119+I119+J119+K119+L119+M119+N119+O119+P119+Q119+R119+S119+T119+U119+V119+W119</f>
-        <v>280290.24</v>
+        <v>363966.37</v>
       </c>
     </row>
     <row r="120" spans="1:24" ht="16">
@@ -7605,13 +7695,13 @@
         <f>V112+V113+V114+V115+V116+V117+V118+V119+V120</f>
         <v>61228.07</v>
       </c>
-      <c r="W121" s="49">
+      <c r="W121" s="48">
         <f>W112+W113+W114+W115+W116+W117+W118+W119+W120</f>
-        <v>0.0</v>
+        <v>150289.37</v>
       </c>
       <c r="X121" s="49">
         <f>B121+C121+D121+E121+F121+G121+H121+I121+J121+K121+L121+M121+N121+O121+P121+Q121+R121+S121+T121+U121+V121+W121</f>
-        <v>1078492.7200000002</v>
+        <v>1228782.0900000003</v>
       </c>
     </row>
     <row r="122" spans="1:24" ht="16">
@@ -7673,12 +7763,12 @@
         <v>15.16</v>
       </c>
       <c r="V122" s="47">
-        <v>2388.07</v>
+        <v>2668.07</v>
       </c>
       <c r="W122" s="46"/>
       <c r="X122" s="47">
         <f>B122+C122+D122+E122+F122+G122+H122+I122+J122+K122+L122+M122+N122+O122+P122+Q122+R122+S122+T122+U122+V122+W122</f>
-        <v>20991.140000000003</v>
+        <v>21271.140000000003</v>
       </c>
     </row>
     <row r="123" spans="1:24" ht="16">
@@ -7800,15 +7890,15 @@
       </c>
       <c r="V124" s="48">
         <f>V18+V19+V20+V30+V35+V36+V37+V54+V55+V56+V57+V58+V61+V62+V63+V64+V65+V74+V75+V81+V82+V83+V88+V89+V90+V91+V92+V105+V106+V111+V121+V122+V123</f>
-        <v>271361.41000000003</v>
-      </c>
-      <c r="W124" s="49">
+        <v>278353.54000000004</v>
+      </c>
+      <c r="W124" s="48">
         <f>W18+W19+W20+W30+W35+W36+W37+W54+W55+W56+W57+W58+W61+W62+W63+W64+W65+W74+W75+W81+W82+W83+W88+W89+W90+W91+W92+W105+W106+W111+W121+W122+W123</f>
-        <v>0.0</v>
+        <v>347044.97</v>
       </c>
       <c r="X124" s="49">
         <f>B124+C124+D124+E124+F124+G124+H124+I124+J124+K124+L124+M124+N124+O124+P124+Q124+R124+S124+T124+U124+V124+W124</f>
-        <v>3776100.0600000005</v>
+        <v>4130137.16</v>
       </c>
     </row>
     <row r="125" spans="1:24" ht="16">
@@ -7897,15 +7987,15 @@
       </c>
       <c r="V125" s="48">
         <f>V17-V124</f>
-        <v>108777.6399999999</v>
-      </c>
-      <c r="W125" s="49">
+        <v>100835.5099999999</v>
+      </c>
+      <c r="W125" s="48">
         <f>W17-W124</f>
-        <v>0.0</v>
+        <v>-88272.91000000003</v>
       </c>
       <c r="X125" s="49">
         <f>B125+C125+D125+E125+F125+G125+H125+I125+J125+K125+L125+M125+N125+O125+P125+Q125+R125+S125+T125+U125+V125+W125</f>
-        <v>727046.8299999996</v>
+        <v>630831.7899999996</v>
       </c>
     </row>
     <row r="126" spans="1:23" ht="16">
@@ -8309,15 +8399,15 @@
       </c>
       <c r="V131" s="48">
         <f>V125+V130</f>
-        <v>108777.6399999999</v>
-      </c>
-      <c r="W131" s="49">
+        <v>100835.5099999999</v>
+      </c>
+      <c r="W131" s="48">
         <f>W125+W130</f>
-        <v>0.0</v>
+        <v>-88272.91000000003</v>
       </c>
       <c r="X131" s="49">
         <f>B131+C131+D131+E131+F131+G131+H131+I131+J131+K131+L131+M131+N131+O131+P131+Q131+R131+S131+T131+U131+V131+W131</f>
-        <v>803686.5399999997</v>
+        <v>707471.4999999997</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="16">
